--- a/Use-Case_Description--Listen_and_View.xlsx
+++ b/Use-Case_Description--Listen_and_View.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950F5440-690F-4D32-832D-7272B6B6EA7C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A871D6B5-095F-49A9-BA85-2E4C2EE8E4B7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="930" windowWidth="18930" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="150" yWindow="70" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Use-Case Name</t>
   </si>
@@ -156,40 +156,68 @@
     <t>Listen to Audio and View Visualizations and Annotations</t>
   </si>
   <si>
-    <t>A Listener / Viewer requests to listen to audio and view visualizations and annotations</t>
-  </si>
-  <si>
-    <t>Listener / Viewer of Audio and Visualizations and Annotations</t>
-  </si>
-  <si>
-    <t>A database must contain a set of audio and visualizations and annotations.</t>
-  </si>
-  <si>
-    <t>The Listener / Viewer is presented with the Listening and Viewing App.</t>
-  </si>
-  <si>
-    <t>1. The Listener / Viewer requests to listen to audio and view visualizations and annotations in a set.
-2. The system provides a menu of titles of sets of audio and visualizations and annotations.
-3. The Listener / Viewer selects a set.
-4. The system provides to the Listener / Viewer the Listening and Viewing App corresponding to the selected set.</t>
-  </si>
-  <si>
-    <t>The Listener / Viewer is presented with a menu of titles of sets of audio and visualizations and annotations.
-The Listener / Viewer selects a set.
-The system presents to the Listener / Viewer the Listening and Viewing App corresponding to the selected set.</t>
-  </si>
-  <si>
-    <t>(4) Present Listening and Viewing App</t>
-  </si>
-  <si>
-    <t>System Diagram, Use Case Description for "Present Listening and Viewing App"</t>
-  </si>
-  <si>
-    <t>(4) Listening and Viewing App for the selected set of audio and visualizations and annotations</t>
-  </si>
-  <si>
-    <t>Listener / Viewer: (1) Request to listen to audio and view visualizations and annotations
-Listener / Viewer: (3) Choice of set of audio and visualizations and annotations</t>
+    <r>
+      <t xml:space="preserve">A Listener / Viewer requests to listen to audio and view visualizations and annotations
+associated with an </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>amalgamation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for which they have permission to listen and view.</t>
+    </r>
+  </si>
+  <si>
+    <t>System Description</t>
+  </si>
+  <si>
+    <t>Definitions</t>
+  </si>
+  <si>
+    <t>Amalgamation: Audio signal, rests, notes, and the start times and durations of rests and notes</t>
+  </si>
+  <si>
+    <t>Listener / Viewer</t>
+  </si>
+  <si>
+    <t>The system presents to the Listener / Viewer an amalgamation for which they have permission to listen and view.</t>
+  </si>
+  <si>
+    <t>At least one audio file for which the Listener / Viewer has permission to listen / view has been processed.</t>
+  </si>
+  <si>
+    <t>The Listener / Viewer is presented with the amalgamation.</t>
+  </si>
+  <si>
+    <t>1. The Listener / Viewer signals desire to listen / view an amalgamation for which they have permission.
+2. The system provides to the Listener / Viewer the set of all amalgamations for which the Listener / Viewer
+has permission to listen / view.
+3. The Listener / Viewer requests to listen to audio and view visualizations and annotations
+in an amalgamation for which they have permission to listen / view.
+4. The system provides to the Listener / Viewer the requested amalgamation.</t>
+  </si>
+  <si>
+    <t>Listener / Viewer: (1) Signal desire to listen / view an amalgamation.
+Listener / Viewer: (3) Request to listen to audio and view visualizations in an amalgamation.</t>
+  </si>
+  <si>
+    <t>(2) Set of all amalgamations for which the Listener / Viewer has permission to listen / view.
+(4) Requested amalgamation.</t>
   </si>
 </sst>
 </file>
@@ -612,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D07CAF-1D8C-45B6-9922-376743399D2A}">
-  <dimension ref="A2:D34"/>
+  <dimension ref="A2:D35"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36" style="2" bestFit="1" customWidth="1"/>
@@ -679,7 +707,7 @@
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="8" t="s">
@@ -691,13 +719,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -713,7 +741,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>34</v>
@@ -724,7 +752,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>35</v>
@@ -741,12 +769,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>36</v>
@@ -765,7 +793,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>17</v>
@@ -776,7 +804,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>18</v>
@@ -793,12 +821,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>20</v>
@@ -824,17 +852,26 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="10"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C27" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.35">
-      <c r="D34" s="9"/>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D35" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Use-Case_Description--Listen_and_View.xlsx
+++ b/Use-Case_Description--Listen_and_View.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A871D6B5-095F-49A9-BA85-2E4C2EE8E4B7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFCCECA-3FA3-4A1A-9E14-55DF7B441950}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="70" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="80" yWindow="110" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -151,9 +151,6 @@
   </si>
   <si>
     <t>Description of Value</t>
-  </si>
-  <si>
-    <t>Listen to Audio and View Visualizations and Annotations</t>
   </si>
   <si>
     <r>
@@ -218,6 +215,9 @@
   <si>
     <t>(2) Set of all amalgamations for which the Listener / Viewer has permission to listen / view.
 (4) Requested amalgamation.</t>
+  </si>
+  <si>
+    <t>Listen and View</t>
   </si>
 </sst>
 </file>
@@ -657,7 +657,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -686,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>2</v>
@@ -708,7 +708,7 @@
         <v>24</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>33</v>
@@ -719,7 +719,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>8</v>
@@ -730,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -741,7 +741,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>34</v>
@@ -752,7 +752,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>35</v>
@@ -774,7 +774,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>36</v>
@@ -804,7 +804,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>18</v>
@@ -815,7 +815,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>19</v>
@@ -826,7 +826,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>20</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="C26" s="10"/>
     </row>

--- a/Use-Case_Description--Listen_and_View.xlsx
+++ b/Use-Case_Description--Listen_and_View.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFCCECA-3FA3-4A1A-9E14-55DF7B441950}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD431726-E28C-4559-B985-DD6FA097905D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="110" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="4560" yWindow="930" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>Use-Case Name</t>
   </si>
@@ -218,6 +218,9 @@
   </si>
   <si>
     <t>Listen and View</t>
+  </si>
+  <si>
+    <t>Grant Permission</t>
   </si>
 </sst>
 </file>
@@ -793,7 +796,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>17</v>

--- a/Use-Case_Description--Listen_and_View.xlsx
+++ b/Use-Case_Description--Listen_and_View.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD431726-E28C-4559-B985-DD6FA097905D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B282B651-2C19-4964-9453-E7CBFB0E32AF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="930" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="170" yWindow="130" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Use-Case Name</t>
   </si>
@@ -151,6 +151,21 @@
   </si>
   <si>
     <t>Description of Value</t>
+  </si>
+  <si>
+    <t>System Description</t>
+  </si>
+  <si>
+    <t>Definitions</t>
+  </si>
+  <si>
+    <t>Listener / Viewer</t>
+  </si>
+  <si>
+    <t>At least one audio file for which the Listener / Viewer has permission to listen / view has been processed.</t>
+  </si>
+  <si>
+    <t>Listen and View</t>
   </si>
   <si>
     <r>
@@ -166,7 +181,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>amalgamation</t>
+      <t>annotated audio signal</t>
     </r>
     <r>
       <rPr>
@@ -180,47 +195,29 @@
     </r>
   </si>
   <si>
-    <t>System Description</t>
-  </si>
-  <si>
-    <t>Definitions</t>
-  </si>
-  <si>
-    <t>Amalgamation: Audio signal, rests, notes, and the start times and durations of rests and notes</t>
-  </si>
-  <si>
-    <t>Listener / Viewer</t>
-  </si>
-  <si>
-    <t>The system presents to the Listener / Viewer an amalgamation for which they have permission to listen and view.</t>
-  </si>
-  <si>
-    <t>At least one audio file for which the Listener / Viewer has permission to listen / view has been processed.</t>
-  </si>
-  <si>
-    <t>The Listener / Viewer is presented with the amalgamation.</t>
-  </si>
-  <si>
-    <t>1. The Listener / Viewer signals desire to listen / view an amalgamation for which they have permission.
-2. The system provides to the Listener / Viewer the set of all amalgamations for which the Listener / Viewer
+    <t>The system presents to the Listener / Viewer an annotated audio signal for which they have permission to listen and view.</t>
+  </si>
+  <si>
+    <t>The Listener / Viewer is presented with the annotated audio signal.</t>
+  </si>
+  <si>
+    <t>1. The Listener / Viewer signals desire to listen / view an annotated audio signal for which they have permission.
+2. The system provides to the Listener / Viewer the set of all annotated audio signals for which the Listener / Viewer
 has permission to listen / view.
 3. The Listener / Viewer requests to listen to audio and view visualizations and annotations
-in an amalgamation for which they have permission to listen / view.
-4. The system provides to the Listener / Viewer the requested amalgamation.</t>
-  </si>
-  <si>
-    <t>Listener / Viewer: (1) Signal desire to listen / view an amalgamation.
-Listener / Viewer: (3) Request to listen to audio and view visualizations in an amalgamation.</t>
-  </si>
-  <si>
-    <t>(2) Set of all amalgamations for which the Listener / Viewer has permission to listen / view.
-(4) Requested amalgamation.</t>
-  </si>
-  <si>
-    <t>Listen and View</t>
-  </si>
-  <si>
-    <t>Grant Permission</t>
+in an annotated audio signal for which they have permission to listen / view.
+4. The system provides to the Listener / Viewer the requested annotated audio signal.</t>
+  </si>
+  <si>
+    <t>Listener / Viewer: (1) Signal desire to listen / view an annotated audio signal.
+Listener / Viewer: (3) Request to listen to audio and view visualizations in an annotated audio signal.</t>
+  </si>
+  <si>
+    <t>(2) Set of all annotated audio signal for which the Listener / Viewer has permission to listen / view.
+(4) Requested annotated audio signal.</t>
+  </si>
+  <si>
+    <t>Annotated audio signal: Audio signal, rests, notes, and the start times and durations of rests and notes</t>
   </si>
 </sst>
 </file>
@@ -660,7 +657,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -689,7 +686,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>2</v>
@@ -711,7 +708,7 @@
         <v>24</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>33</v>
@@ -722,7 +719,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>8</v>
@@ -733,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>9</v>
@@ -744,7 +741,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>34</v>
@@ -772,7 +769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -796,7 +793,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>17</v>
@@ -807,7 +804,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>18</v>
@@ -855,10 +852,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C26" s="10"/>
     </row>
